--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
@@ -397,25 +397,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.672081007344369</v>
+        <v>0.6720810073443689</v>
       </c>
       <c r="C2">
-        <v>0.723168665304872</v>
+        <v>0.7092559956622544</v>
       </c>
       <c r="D2">
         <v>1.487638583328825</v>
       </c>
       <c r="E2">
-        <v>0.701551440642474</v>
+        <v>0.7002043273743609</v>
       </c>
       <c r="F2">
         <v>0.6827356175898305</v>
       </c>
       <c r="G2">
-        <v>0.7536277294702586</v>
+        <v>0.7290632462805418</v>
       </c>
       <c r="H2">
-        <v>0.7020555702255472</v>
+        <v>0.7006890313337328</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -423,25 +423,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.7015778299709426</v>
+        <v>0.7015778299709424</v>
       </c>
       <c r="C3">
-        <v>0.7290325917100523</v>
+        <v>0.7171446371773404</v>
       </c>
       <c r="D3">
         <v>1.408310378582805</v>
       </c>
       <c r="E3">
-        <v>0.7078925321183754</v>
+        <v>0.7063599027711679</v>
       </c>
       <c r="F3">
         <v>0.7044409774657061</v>
       </c>
       <c r="G3">
-        <v>0.7570069272544382</v>
+        <v>0.7333613288730276</v>
       </c>
       <c r="H3">
-        <v>0.7081315057986718</v>
+        <v>0.706588512718861</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -449,25 +449,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.6168906973569016</v>
+        <v>0.6168906973569015</v>
       </c>
       <c r="C4">
-        <v>0.7534191860044763</v>
+        <v>0.7103663845345167</v>
       </c>
       <c r="D4">
         <v>1.005622767603824</v>
       </c>
       <c r="E4">
-        <v>0.6933055670541942</v>
+        <v>0.6919681603173675</v>
       </c>
       <c r="F4">
         <v>0.6296424307716176</v>
       </c>
       <c r="G4">
-        <v>0.7349999972699376</v>
+        <v>0.7046267294810441</v>
       </c>
       <c r="H4">
-        <v>0.693547048612115</v>
+        <v>0.6921960473754905</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>0.7373143177077819</v>
       </c>
       <c r="C5">
-        <v>0.7813154601969541</v>
+        <v>0.7497438449623276</v>
       </c>
       <c r="D5">
         <v>0.4406486889174661</v>
       </c>
       <c r="E5">
-        <v>0.7117190287704004</v>
+        <v>0.7097830060621994</v>
       </c>
       <c r="F5">
         <v>0.7328281215101273</v>
       </c>
       <c r="G5">
-        <v>0.7577576192567733</v>
+        <v>0.7380320129858585</v>
       </c>
       <c r="H5">
-        <v>0.7115205004370663</v>
+        <v>0.7095929480110589</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>0.7264082756098442</v>
       </c>
       <c r="C6">
-        <v>0.7788966201490836</v>
+        <v>0.7442507980091263</v>
       </c>
       <c r="D6">
         <v>0.2990603850972823</v>
       </c>
       <c r="E6">
-        <v>0.709718135770374</v>
+        <v>0.7077923235746036</v>
       </c>
       <c r="F6">
         <v>0.7222865935179038</v>
       </c>
       <c r="G6">
-        <v>0.7497759552333861</v>
+        <v>0.7291236296109174</v>
       </c>
       <c r="H6">
-        <v>0.7094697801252308</v>
+        <v>0.7075523321511903</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -530,22 +530,22 @@
         <v>0.7581868676151399</v>
       </c>
       <c r="C7">
-        <v>0.800507487256723</v>
+        <v>0.7634258695380866</v>
       </c>
       <c r="D7">
         <v>0.4173120270607643</v>
       </c>
       <c r="E7">
-        <v>0.7201921729891058</v>
+        <v>0.7182202071614885</v>
       </c>
       <c r="F7">
         <v>0.7533715401581433</v>
       </c>
       <c r="G7">
-        <v>0.7729662477052786</v>
+        <v>0.7506844926718718</v>
       </c>
       <c r="H7">
-        <v>0.7199951685803621</v>
+        <v>0.7180318597321101</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -553,25 +553,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.6972172193191215</v>
+        <v>0.6972172193191213</v>
       </c>
       <c r="C8">
-        <v>0.606126462360837</v>
+        <v>0.6528399286774035</v>
       </c>
       <c r="D8">
         <v>0.3108452978446444</v>
       </c>
       <c r="E8">
-        <v>0.6911889526972824</v>
+        <v>0.6940331407047413</v>
       </c>
       <c r="F8">
         <v>0.6928378562941038</v>
       </c>
       <c r="G8">
-        <v>0.6135086850507573</v>
+        <v>0.6524168076416768</v>
       </c>
       <c r="H8">
-        <v>0.6909898094845424</v>
+        <v>0.693839945186039</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>0.7652800459638724</v>
       </c>
       <c r="C9">
-        <v>0.75941793639796</v>
+        <v>0.7359835305854562</v>
       </c>
       <c r="D9">
         <v>0.5882943898208607</v>
       </c>
       <c r="E9">
-        <v>0.7174256421780868</v>
+        <v>0.7155647131582599</v>
       </c>
       <c r="F9">
         <v>0.7605472385025487</v>
       </c>
       <c r="G9">
-        <v>0.7399637731815616</v>
+        <v>0.7300219831045288</v>
       </c>
       <c r="H9">
-        <v>0.7173079007704015</v>
+        <v>0.7154505454293572</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>0.7614197283363611</v>
       </c>
       <c r="C10">
-        <v>0.7962211528660872</v>
+        <v>0.7610162011337268</v>
       </c>
       <c r="D10">
         <v>1.107204519682487</v>
       </c>
       <c r="E10">
-        <v>0.7192211507500265</v>
+        <v>0.7173122770036456</v>
       </c>
       <c r="F10">
         <v>0.7614022543224178</v>
       </c>
       <c r="G10">
-        <v>0.7888481291569622</v>
+        <v>0.7604444292657107</v>
       </c>
       <c r="H10">
-        <v>0.7195665583922763</v>
+        <v>0.7176657096921482</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -631,25 +631,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.7536675349904853</v>
+        <v>0.7536675349904851</v>
       </c>
       <c r="C11">
-        <v>0.7975478595879739</v>
+        <v>0.7627958820574808</v>
       </c>
       <c r="D11">
         <v>0.988328355728557</v>
       </c>
       <c r="E11">
-        <v>0.7198608049094366</v>
+        <v>0.7179885696935229</v>
       </c>
       <c r="F11">
         <v>0.7534768782313206</v>
       </c>
       <c r="G11">
-        <v>0.7865039493820257</v>
+        <v>0.7567833805556493</v>
       </c>
       <c r="H11">
-        <v>0.7200733864287132</v>
+        <v>0.7182092897024704</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>0.659795161260209</v>
       </c>
       <c r="C12">
-        <v>0.8004431530328775</v>
+        <v>0.759398913530363</v>
       </c>
       <c r="D12">
         <v>0.430288162070488</v>
       </c>
       <c r="E12">
-        <v>0.7135288818346025</v>
+        <v>0.7115593736496669</v>
       </c>
       <c r="F12">
         <v>0.6614578653373322</v>
       </c>
       <c r="G12">
-        <v>0.7717791700251481</v>
+        <v>0.7454720414069178</v>
       </c>
       <c r="H12">
-        <v>0.7133225942756337</v>
+        <v>0.711360375947285</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -683,25 +683,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.7569554584173224</v>
+        <v>0.7569554584173221</v>
       </c>
       <c r="C13">
-        <v>0.7952743077948078</v>
+        <v>0.7590621141496083</v>
       </c>
       <c r="D13">
         <v>0.9258688481323134</v>
       </c>
       <c r="E13">
-        <v>0.7183637077962255</v>
+        <v>0.7164493622181854</v>
       </c>
       <c r="F13">
         <v>0.7559454293592841</v>
       </c>
       <c r="G13">
-        <v>0.7830607682763813</v>
+        <v>0.754178808815176</v>
       </c>
       <c r="H13">
-        <v>0.7186178328993582</v>
+        <v>0.7167114124602449</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
@@ -403,25 +403,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.6720810073443689</v>
+        <v>0.550543004818621</v>
       </c>
       <c r="C2">
-        <v>0.7092559956622544</v>
+        <v>0.5809953305784216</v>
       </c>
       <c r="D2">
-        <v>1.487638583328825</v>
+        <v>1.218616516163972</v>
       </c>
       <c r="E2">
-        <v>0.7002043273743609</v>
+        <v>0.5735805508072606</v>
       </c>
       <c r="F2">
-        <v>0.6827356175898305</v>
+        <v>0.5592708532113102</v>
       </c>
       <c r="G2">
-        <v>0.7290632462805418</v>
+        <v>0.5972206712046595</v>
       </c>
       <c r="H2">
-        <v>0.7006890313337328</v>
+        <v>0.5739776017152972</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.7015778299709424</v>
+        <v>0.5926532590853557</v>
       </c>
       <c r="C3">
-        <v>0.7171446371773404</v>
+        <v>0.6058032171232366</v>
       </c>
       <c r="D3">
-        <v>1.408310378582805</v>
+        <v>1.189660932851027</v>
       </c>
       <c r="E3">
-        <v>0.7063599027711679</v>
+        <v>0.5966928836418423</v>
       </c>
       <c r="F3">
-        <v>0.7044409774657061</v>
+        <v>0.5950718841067367</v>
       </c>
       <c r="G3">
-        <v>0.7333613288730276</v>
+        <v>0.6195021608105384</v>
       </c>
       <c r="H3">
-        <v>0.706588512718861</v>
+        <v>0.5968860003920754</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -455,25 +455,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.6168906973569015</v>
+        <v>0.5015934652661029</v>
       </c>
       <c r="C4">
-        <v>0.7103663845345167</v>
+        <v>0.5775984918460773</v>
       </c>
       <c r="D4">
-        <v>1.005622767603824</v>
+        <v>0.8176712842551797</v>
       </c>
       <c r="E4">
-        <v>0.6919681603173675</v>
+        <v>0.5626389064943087</v>
       </c>
       <c r="F4">
-        <v>0.6296424307716176</v>
+        <v>0.5119618922484546</v>
       </c>
       <c r="G4">
-        <v>0.7046267294810441</v>
+        <v>0.5729315816786221</v>
       </c>
       <c r="H4">
-        <v>0.6921960473754905</v>
+        <v>0.5628242013280013</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -481,25 +481,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.7373143177077819</v>
+        <v>0.1837579027104534</v>
       </c>
       <c r="C5">
-        <v>0.7497438449623276</v>
+        <v>0.1868556641469578</v>
       </c>
       <c r="D5">
-        <v>0.4406486889174661</v>
+        <v>0.1098211128726193</v>
       </c>
       <c r="E5">
-        <v>0.7097830060621994</v>
+        <v>0.1768963838637989</v>
       </c>
       <c r="F5">
-        <v>0.7328281215101273</v>
+        <v>0.1826398259491184</v>
       </c>
       <c r="G5">
-        <v>0.7380320129858585</v>
+        <v>0.1839367710382712</v>
       </c>
       <c r="H5">
-        <v>0.7095929480110589</v>
+        <v>0.1768490164547685</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -507,25 +507,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.7264082756098442</v>
+        <v>0.6854489898666445</v>
       </c>
       <c r="C6">
-        <v>0.7442507980091263</v>
+        <v>0.7022854430926124</v>
       </c>
       <c r="D6">
-        <v>0.2990603850972823</v>
+        <v>0.2821975544014355</v>
       </c>
       <c r="E6">
-        <v>0.7077923235746036</v>
+        <v>0.6678827176387452</v>
       </c>
       <c r="F6">
-        <v>0.7222865935179038</v>
+        <v>0.6815597131040694</v>
       </c>
       <c r="G6">
-        <v>0.7291236296109174</v>
+        <v>0.6880112358096764</v>
       </c>
       <c r="H6">
-        <v>0.7075523321511903</v>
+        <v>0.6676562583812192</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -533,25 +533,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.7581868676151399</v>
+        <v>0.6547977493039842</v>
       </c>
       <c r="C7">
-        <v>0.7634258695380866</v>
+        <v>0.659322341873802</v>
       </c>
       <c r="D7">
-        <v>0.4173120270607643</v>
+        <v>0.3604058415524781</v>
       </c>
       <c r="E7">
-        <v>0.7182202071614885</v>
+        <v>0.6202810880031034</v>
       </c>
       <c r="F7">
-        <v>0.7533715401581433</v>
+        <v>0.6506390574093054</v>
       </c>
       <c r="G7">
-        <v>0.7506844926718718</v>
+        <v>0.6483184254893437</v>
       </c>
       <c r="H7">
-        <v>0.7180318597321101</v>
+        <v>0.6201184243140953</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -559,25 +559,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.6972172193191213</v>
+        <v>0.174251373063965</v>
       </c>
       <c r="C8">
-        <v>0.6528399286774035</v>
+        <v>0.1631604194659894</v>
       </c>
       <c r="D8">
-        <v>0.3108452978446444</v>
+        <v>0.07768772551659349</v>
       </c>
       <c r="E8">
-        <v>0.6940331407047413</v>
+        <v>0.1734555951412092</v>
       </c>
       <c r="F8">
-        <v>0.6928378562941038</v>
+        <v>0.1731568647828872</v>
       </c>
       <c r="G8">
-        <v>0.6524168076416768</v>
+        <v>0.1630546713298208</v>
       </c>
       <c r="H8">
-        <v>0.693839945186039</v>
+        <v>0.17340731092867</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -585,25 +585,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.7652800459638724</v>
+        <v>0.6556239312220005</v>
       </c>
       <c r="C9">
-        <v>0.7359835305854562</v>
+        <v>0.6305252804930227</v>
       </c>
       <c r="D9">
-        <v>0.5882943898208607</v>
+        <v>0.5039983501522117</v>
       </c>
       <c r="E9">
-        <v>0.7155647131582599</v>
+        <v>0.6130322523876557</v>
       </c>
       <c r="F9">
-        <v>0.7605472385025487</v>
+        <v>0.6515692824043876</v>
       </c>
       <c r="G9">
-        <v>0.7300219831045288</v>
+        <v>0.6254179564275042</v>
       </c>
       <c r="H9">
-        <v>0.7154505454293572</v>
+        <v>0.6129344436238746</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -611,25 +611,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.7614197283363611</v>
+        <v>0.1914552496105879</v>
       </c>
       <c r="C10">
-        <v>0.7610162011337268</v>
+        <v>0.1913537846781337</v>
       </c>
       <c r="D10">
-        <v>1.107204519682487</v>
+        <v>0.2784011364519547</v>
       </c>
       <c r="E10">
-        <v>0.7173122770036456</v>
+        <v>0.1803646476858877</v>
       </c>
       <c r="F10">
-        <v>0.7614022543224178</v>
+        <v>0.1914508558556369</v>
       </c>
       <c r="G10">
-        <v>0.7604444292657107</v>
+        <v>0.1912100154512048</v>
       </c>
       <c r="H10">
-        <v>0.7176657096921482</v>
+        <v>0.1804535165988927</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -637,25 +637,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.7536675349904851</v>
+        <v>0.1823389197557625</v>
       </c>
       <c r="C11">
-        <v>0.7627958820574808</v>
+        <v>0.1845473908203582</v>
       </c>
       <c r="D11">
-        <v>0.988328355728557</v>
+        <v>0.2391116989665864</v>
       </c>
       <c r="E11">
-        <v>0.7179885696935229</v>
+        <v>0.1737069120226265</v>
       </c>
       <c r="F11">
-        <v>0.7534768782313206</v>
+        <v>0.1822927931204808</v>
       </c>
       <c r="G11">
-        <v>0.7567833805556493</v>
+        <v>0.1830927533602378</v>
       </c>
       <c r="H11">
-        <v>0.7182092897024704</v>
+        <v>0.1737603120247911</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -663,25 +663,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.659795161260209</v>
+        <v>0.6670383477510234</v>
       </c>
       <c r="C12">
-        <v>0.759398913530363</v>
+        <v>0.7677355432521035</v>
       </c>
       <c r="D12">
-        <v>0.430288162070488</v>
+        <v>0.4350118363040388</v>
       </c>
       <c r="E12">
-        <v>0.7115593736496669</v>
+        <v>0.7193708241501335</v>
       </c>
       <c r="F12">
-        <v>0.6614578653373322</v>
+        <v>0.6687193048806347</v>
       </c>
       <c r="G12">
-        <v>0.7454720414069178</v>
+        <v>0.7536557828718982</v>
       </c>
       <c r="H12">
-        <v>0.711360375947285</v>
+        <v>0.7191696418644836</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -689,25 +689,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.7569554584173221</v>
+        <v>0.1902093203202502</v>
       </c>
       <c r="C13">
-        <v>0.7590621141496083</v>
+        <v>0.1907386850940041</v>
       </c>
       <c r="D13">
-        <v>0.9258688481323134</v>
+        <v>0.2326542233768378</v>
       </c>
       <c r="E13">
-        <v>0.7164493622181854</v>
+        <v>0.180030865377903</v>
       </c>
       <c r="F13">
-        <v>0.7559454293592841</v>
+        <v>0.1899555181466919</v>
       </c>
       <c r="G13">
-        <v>0.754178808815176</v>
+        <v>0.1895115981125314</v>
       </c>
       <c r="H13">
-        <v>0.7167114124602449</v>
+        <v>0.1800967139002668</v>
       </c>
     </row>
   </sheetData>
